--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,15 +434,25 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -460,22 +470,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.25607</v>
+        <v>17.57434</v>
       </c>
       <c r="D2" t="n">
-        <v>16.51685</v>
+        <v>17.08599</v>
       </c>
       <c r="E2" t="n">
-        <v>16.89663</v>
+        <v>17.17028</v>
       </c>
       <c r="F2" t="n">
-        <v>43.51559</v>
+        <v>57.16303</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05031</v>
+        <v>44.60046</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86607</v>
+        <v>87.61716</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.05125</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.85302</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +501,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.04685</v>
+        <v>17.45224</v>
       </c>
       <c r="D3" t="n">
-        <v>16.54739</v>
+        <v>16.89517</v>
       </c>
       <c r="E3" t="n">
-        <v>17.00352</v>
+        <v>17.00443</v>
       </c>
       <c r="F3" t="n">
-        <v>42.82171</v>
+        <v>56.67433</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0518</v>
+        <v>44.39298</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86166</v>
+        <v>86.3866</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.05158</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.84498</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +532,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.13133</v>
+        <v>17.2064</v>
       </c>
       <c r="D4" t="n">
-        <v>16.90264</v>
+        <v>16.74568</v>
       </c>
       <c r="E4" t="n">
-        <v>17.26242</v>
+        <v>16.92083</v>
       </c>
       <c r="F4" t="n">
-        <v>43.02643</v>
+        <v>56.97432</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05102</v>
+        <v>43.20317</v>
       </c>
       <c r="H4" t="n">
-        <v>1.87587</v>
+        <v>87.16656999999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.05184</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.86227</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +563,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.20526</v>
+        <v>17.22155</v>
       </c>
       <c r="D5" t="n">
-        <v>17.11065</v>
+        <v>16.88654</v>
       </c>
       <c r="E5" t="n">
-        <v>17.08591</v>
+        <v>17.00089</v>
       </c>
       <c r="F5" t="n">
-        <v>44.85777</v>
+        <v>56.22198</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05014</v>
+        <v>43.02999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.84376</v>
+        <v>86.97709999999999</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05182</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.82594</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +594,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.20003</v>
+        <v>17.28406</v>
       </c>
       <c r="D6" t="n">
-        <v>16.76732</v>
+        <v>16.88558</v>
       </c>
       <c r="E6" t="n">
-        <v>17.40051</v>
+        <v>16.89163</v>
       </c>
       <c r="F6" t="n">
-        <v>42.80838</v>
+        <v>57.16045</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05303</v>
+        <v>42.76181</v>
       </c>
       <c r="H6" t="n">
-        <v>1.85414</v>
+        <v>84.60384000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05321</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.84001</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +625,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.91362</v>
+        <v>17.26299</v>
       </c>
       <c r="D7" t="n">
-        <v>16.91891</v>
+        <v>16.83095</v>
       </c>
       <c r="E7" t="n">
-        <v>16.70799</v>
+        <v>17.08674</v>
       </c>
       <c r="F7" t="n">
-        <v>44.05037</v>
+        <v>55.60691</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05146</v>
+        <v>42.99875</v>
       </c>
       <c r="H7" t="n">
-        <v>1.88743</v>
+        <v>88.28557000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.05083</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.87246</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +656,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.23101</v>
+        <v>17.16633</v>
       </c>
       <c r="D8" t="n">
-        <v>17.0286</v>
+        <v>16.76025</v>
       </c>
       <c r="E8" t="n">
-        <v>17.31734</v>
+        <v>17.07871</v>
       </c>
       <c r="F8" t="n">
-        <v>42.83258</v>
+        <v>57.19164</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05138</v>
+        <v>43.53012</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8568</v>
+        <v>86.77812</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05175</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.81368</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +687,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.18583</v>
+        <v>17.18102</v>
       </c>
       <c r="D9" t="n">
-        <v>16.87711</v>
+        <v>17.0399</v>
       </c>
       <c r="E9" t="n">
-        <v>17.04614</v>
+        <v>17.17675</v>
       </c>
       <c r="F9" t="n">
-        <v>42.95375</v>
+        <v>55.64223</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05174</v>
+        <v>43.81257</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8426</v>
+        <v>88.25636</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.05112</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.83294</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +718,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.43145</v>
+        <v>17.28227</v>
       </c>
       <c r="D10" t="n">
-        <v>16.93627</v>
+        <v>16.76352</v>
       </c>
       <c r="E10" t="n">
-        <v>16.95824</v>
+        <v>17.17645</v>
       </c>
       <c r="F10" t="n">
-        <v>44.09531</v>
+        <v>57.49866</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05154</v>
+        <v>42.59004</v>
       </c>
       <c r="H10" t="n">
-        <v>1.89741</v>
+        <v>85.99408</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05278</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.85586</v>
       </c>
     </row>
     <row r="11">
@@ -696,15 +760,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -722,22 +796,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.31105</v>
+        <v>16.92398</v>
       </c>
       <c r="D12" t="n">
-        <v>17.10083</v>
+        <v>16.71389</v>
       </c>
       <c r="E12" t="n">
-        <v>17.10667</v>
+        <v>16.74018</v>
       </c>
       <c r="F12" t="n">
-        <v>42.59602</v>
+        <v>56.73983</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05207</v>
+        <v>43.18271</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8749</v>
+        <v>86.90927000000001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.05202</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.81936</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +827,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.13835</v>
+        <v>16.9847</v>
       </c>
       <c r="D13" t="n">
-        <v>17.22546</v>
+        <v>16.71654</v>
       </c>
       <c r="E13" t="n">
-        <v>16.81535</v>
+        <v>16.88066</v>
       </c>
       <c r="F13" t="n">
-        <v>43.92479</v>
+        <v>57.32578</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05124</v>
+        <v>43.33667</v>
       </c>
       <c r="H13" t="n">
-        <v>1.81672</v>
+        <v>84.69141</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.05138</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.83865</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +858,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.8048</v>
+        <v>17.04993</v>
       </c>
       <c r="D14" t="n">
-        <v>16.75271</v>
+        <v>16.65553</v>
       </c>
       <c r="E14" t="n">
-        <v>17.03789</v>
+        <v>16.79525</v>
       </c>
       <c r="F14" t="n">
-        <v>43.1073</v>
+        <v>55.66317</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05192</v>
+        <v>44.20997</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8772</v>
+        <v>88.32720999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.05249</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.8331</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +889,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.05594</v>
+        <v>17.04347</v>
       </c>
       <c r="D15" t="n">
-        <v>17.05423</v>
+        <v>16.63682</v>
       </c>
       <c r="E15" t="n">
-        <v>16.7291</v>
+        <v>16.7276</v>
       </c>
       <c r="F15" t="n">
-        <v>43.14634</v>
+        <v>57.48814</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05141</v>
+        <v>43.70441</v>
       </c>
       <c r="H15" t="n">
-        <v>1.85565</v>
+        <v>86.89076</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.05097</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.86197</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +920,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.95924</v>
+        <v>17.25551</v>
       </c>
       <c r="D16" t="n">
-        <v>16.86987</v>
+        <v>16.71985</v>
       </c>
       <c r="E16" t="n">
-        <v>17.11292</v>
+        <v>17.10572</v>
       </c>
       <c r="F16" t="n">
-        <v>43.66617</v>
+        <v>57.13314</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0516</v>
+        <v>44.27782</v>
       </c>
       <c r="H16" t="n">
-        <v>1.85117</v>
+        <v>85.77606</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.05163</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.87193</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +951,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.9695</v>
+        <v>16.8821</v>
       </c>
       <c r="D17" t="n">
-        <v>16.87328</v>
+        <v>16.38958</v>
       </c>
       <c r="E17" t="n">
-        <v>17.25065</v>
+        <v>16.63113</v>
       </c>
       <c r="F17" t="n">
-        <v>43.0015</v>
+        <v>56.5107</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05102</v>
+        <v>42.77873</v>
       </c>
       <c r="H17" t="n">
-        <v>1.86764</v>
+        <v>86.4799</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.05123</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.87145</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +982,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.22823</v>
+        <v>17.2508</v>
       </c>
       <c r="D18" t="n">
-        <v>16.96691</v>
+        <v>16.85415</v>
       </c>
       <c r="E18" t="n">
-        <v>17.13447</v>
+        <v>17.13104</v>
       </c>
       <c r="F18" t="n">
-        <v>42.78906</v>
+        <v>56.75011</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05133</v>
+        <v>43.90414</v>
       </c>
       <c r="H18" t="n">
-        <v>1.82917</v>
+        <v>86.92654</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.05189</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.84528</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +1013,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.09553</v>
+        <v>17.27637</v>
       </c>
       <c r="D19" t="n">
-        <v>16.96463</v>
+        <v>16.78791</v>
       </c>
       <c r="E19" t="n">
-        <v>16.9659</v>
+        <v>17.02388</v>
       </c>
       <c r="F19" t="n">
-        <v>42.95907</v>
+        <v>56.73562</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05216</v>
+        <v>43.43794</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8504</v>
+        <v>85.98969</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.05198</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.81857</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +1044,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.89301</v>
+        <v>17.17022</v>
       </c>
       <c r="D20" t="n">
-        <v>16.90934</v>
+        <v>16.80419</v>
       </c>
       <c r="E20" t="n">
-        <v>16.98198</v>
+        <v>16.84984</v>
       </c>
       <c r="F20" t="n">
-        <v>42.65269</v>
+        <v>56.7611</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05187</v>
+        <v>43.43217</v>
       </c>
       <c r="H20" t="n">
-        <v>1.83785</v>
+        <v>85.31126</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.05084</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.85903</v>
       </c>
     </row>
     <row r="21">
@@ -958,7 +1086,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -970,20 +1103,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SR Pad 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.31206</v>
+        <v>17.36449</v>
       </c>
       <c r="D22" t="n">
-        <v>15.82666</v>
+        <v>15.99956</v>
       </c>
       <c r="E22" t="n">
-        <v>15.71847</v>
+        <v>16.82603</v>
       </c>
       <c r="F22" t="n">
-        <v>259.61385</v>
+        <v>22.50934</v>
+      </c>
+      <c r="G22" t="n">
+        <v>35.26465</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +1129,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.68664</v>
+        <v>16.8045</v>
       </c>
       <c r="D23" t="n">
-        <v>15.99406</v>
+        <v>16.32455</v>
       </c>
       <c r="E23" t="n">
-        <v>16.0077</v>
+        <v>16.35891</v>
       </c>
       <c r="F23" t="n">
-        <v>261.15325</v>
+        <v>21.7994</v>
+      </c>
+      <c r="G23" t="n">
+        <v>35.28469</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1151,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.71788</v>
+        <v>17.09216</v>
       </c>
       <c r="D24" t="n">
-        <v>15.72177</v>
+        <v>16.22338</v>
       </c>
       <c r="E24" t="n">
-        <v>15.68801</v>
+        <v>16.89297</v>
       </c>
       <c r="F24" t="n">
-        <v>263.86877</v>
+        <v>22.12322</v>
+      </c>
+      <c r="G24" t="n">
+        <v>34.67804</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1173,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.86992</v>
+        <v>17.196</v>
       </c>
       <c r="D25" t="n">
-        <v>15.70547</v>
+        <v>15.86105</v>
       </c>
       <c r="E25" t="n">
-        <v>16.0685</v>
+        <v>16.71295</v>
       </c>
       <c r="F25" t="n">
-        <v>260.2352</v>
+        <v>22.0701</v>
+      </c>
+      <c r="G25" t="n">
+        <v>34.59626</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1195,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.19705</v>
+        <v>16.77482</v>
       </c>
       <c r="D26" t="n">
-        <v>15.92173</v>
+        <v>16.3034</v>
       </c>
       <c r="E26" t="n">
-        <v>16.20537</v>
+        <v>16.64208</v>
       </c>
       <c r="F26" t="n">
-        <v>253.53047</v>
+        <v>22.0183</v>
+      </c>
+      <c r="G26" t="n">
+        <v>34.93902</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1217,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.13084</v>
+        <v>17.25406</v>
       </c>
       <c r="D27" t="n">
-        <v>15.8188</v>
+        <v>16.49348</v>
       </c>
       <c r="E27" t="n">
-        <v>15.60528</v>
+        <v>16.73008</v>
       </c>
       <c r="F27" t="n">
-        <v>260.34049</v>
+        <v>21.88889</v>
+      </c>
+      <c r="G27" t="n">
+        <v>34.98936</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1239,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.10197</v>
+        <v>16.99176</v>
       </c>
       <c r="D28" t="n">
-        <v>15.84065</v>
+        <v>16.28182</v>
       </c>
       <c r="E28" t="n">
-        <v>16.25727</v>
+        <v>16.81247</v>
       </c>
       <c r="F28" t="n">
-        <v>266.46434</v>
+        <v>22.38232</v>
+      </c>
+      <c r="G28" t="n">
+        <v>34.94937</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1261,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.09579</v>
+        <v>17.40853</v>
       </c>
       <c r="D29" t="n">
-        <v>15.85247</v>
+        <v>16.57454</v>
       </c>
       <c r="E29" t="n">
-        <v>15.98657</v>
+        <v>16.96517</v>
       </c>
       <c r="F29" t="n">
-        <v>253.00896</v>
+        <v>22.02417</v>
+      </c>
+      <c r="G29" t="n">
+        <v>35.83828</v>
       </c>
     </row>
     <row r="30">
@@ -1126,42 +1283,60 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.13574</v>
+        <v>16.92793</v>
       </c>
       <c r="D30" t="n">
-        <v>16.12686</v>
+        <v>16.41532</v>
       </c>
       <c r="E30" t="n">
-        <v>15.76365</v>
+        <v>16.79454</v>
       </c>
       <c r="F30" t="n">
-        <v>259.66278</v>
+        <v>22.12532</v>
+      </c>
+      <c r="G30" t="n">
+        <v>35.15509</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Rz max</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
+          <t>Rz mean</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mean Stepheight</t>
+          <t>Rz min</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Rz max</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
         </is>
       </c>
     </row>
@@ -1173,23 +1348,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>roughness</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17.13056</v>
+        <v>0.74865</v>
       </c>
       <c r="D32" t="n">
-        <v>16.11751</v>
+        <v>0.08266999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>16.71764</v>
+        <v>0.61877</v>
       </c>
       <c r="F32" t="n">
-        <v>22.16971</v>
+        <v>0.99508</v>
       </c>
       <c r="G32" t="n">
-        <v>35.29995</v>
+        <v>0.11197</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00767</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09483999999999999</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12913</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1383,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17.04326</v>
+        <v>0.75152</v>
       </c>
       <c r="D33" t="n">
-        <v>16.30705</v>
+        <v>0.08372</v>
       </c>
       <c r="E33" t="n">
-        <v>16.75838</v>
+        <v>0.62271</v>
       </c>
       <c r="F33" t="n">
-        <v>22.78706</v>
+        <v>0.99244</v>
       </c>
       <c r="G33" t="n">
-        <v>34.99967</v>
+        <v>0.10976</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00788</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09412</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.1283</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1414,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16.75144</v>
+        <v>0.76851</v>
       </c>
       <c r="D34" t="n">
-        <v>16.55725</v>
+        <v>0.08261</v>
       </c>
       <c r="E34" t="n">
-        <v>16.61384</v>
+        <v>0.6117</v>
       </c>
       <c r="F34" t="n">
-        <v>21.93758</v>
+        <v>0.98192</v>
       </c>
       <c r="G34" t="n">
-        <v>33.79126</v>
+        <v>0.11095</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00778</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09537</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.12946</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1445,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17.25637</v>
+        <v>0.75803</v>
       </c>
       <c r="D35" t="n">
-        <v>16.24114</v>
+        <v>0.08146</v>
       </c>
       <c r="E35" t="n">
-        <v>16.64185</v>
+        <v>0.61114</v>
       </c>
       <c r="F35" t="n">
-        <v>21.96926</v>
+        <v>0.9718</v>
       </c>
       <c r="G35" t="n">
-        <v>34.77573</v>
+        <v>0.1103</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00774</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.0948</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.13037</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1476,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>17.04429</v>
+        <v>0.76065</v>
       </c>
       <c r="D36" t="n">
-        <v>16.31223</v>
+        <v>0.08312</v>
       </c>
       <c r="E36" t="n">
-        <v>16.53094</v>
+        <v>0.61153</v>
       </c>
       <c r="F36" t="n">
-        <v>22.15125</v>
+        <v>0.9998</v>
       </c>
       <c r="G36" t="n">
-        <v>34.35097</v>
+        <v>0.1121</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00773</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09551</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12885</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1507,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.62951</v>
+        <v>0.75573</v>
       </c>
       <c r="D37" t="n">
-        <v>16.5045</v>
+        <v>0.08185000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>16.44371</v>
+        <v>0.62093</v>
       </c>
       <c r="F37" t="n">
-        <v>21.93707</v>
+        <v>0.99922</v>
       </c>
       <c r="G37" t="n">
-        <v>34.2147</v>
+        <v>0.11134</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09454</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12662</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1538,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>17.21221</v>
+        <v>0.75437</v>
       </c>
       <c r="D38" t="n">
-        <v>16.29932</v>
+        <v>0.08151</v>
       </c>
       <c r="E38" t="n">
-        <v>16.66374</v>
+        <v>0.61234</v>
       </c>
       <c r="F38" t="n">
-        <v>21.82765</v>
+        <v>0.98027</v>
       </c>
       <c r="G38" t="n">
-        <v>34.53366</v>
+        <v>0.11175</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09331</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.13002</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1569,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>17.12472</v>
+        <v>0.76319</v>
       </c>
       <c r="D39" t="n">
-        <v>16.37903</v>
+        <v>0.08237999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>16.75947</v>
+        <v>0.61083</v>
       </c>
       <c r="F39" t="n">
-        <v>22.38064</v>
+        <v>0.97836</v>
       </c>
       <c r="G39" t="n">
-        <v>34.4325</v>
+        <v>0.11077</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00777</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09465</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.13082</v>
       </c>
     </row>
     <row r="40">
@@ -1353,843 +1600,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16.7133</v>
+        <v>0.77865</v>
       </c>
       <c r="D40" t="n">
-        <v>16.63555</v>
+        <v>0.08337</v>
       </c>
       <c r="E40" t="n">
-        <v>16.96068</v>
+        <v>0.61419</v>
       </c>
       <c r="F40" t="n">
-        <v>22.34662</v>
+        <v>0.98176</v>
       </c>
       <c r="G40" t="n">
-        <v>34.47198</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Trace 2</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>17.30721</v>
-      </c>
-      <c r="D42" t="n">
-        <v>16.39938</v>
-      </c>
-      <c r="E42" t="n">
-        <v>16.79338</v>
-      </c>
-      <c r="F42" t="n">
-        <v>22.03338</v>
-      </c>
-      <c r="G42" t="n">
-        <v>35.41753</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>17.12718</v>
-      </c>
-      <c r="D43" t="n">
-        <v>16.37684</v>
-      </c>
-      <c r="E43" t="n">
-        <v>16.84539</v>
-      </c>
-      <c r="F43" t="n">
-        <v>22.53238</v>
-      </c>
-      <c r="G43" t="n">
-        <v>33.9152</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>17.49587</v>
-      </c>
-      <c r="D44" t="n">
-        <v>16.06383</v>
-      </c>
-      <c r="E44" t="n">
-        <v>16.82168</v>
-      </c>
-      <c r="F44" t="n">
-        <v>22.10268</v>
-      </c>
-      <c r="G44" t="n">
-        <v>34.20603</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>16.78951</v>
-      </c>
-      <c r="D45" t="n">
-        <v>16.48143</v>
-      </c>
-      <c r="E45" t="n">
-        <v>16.52791</v>
-      </c>
-      <c r="F45" t="n">
-        <v>21.75901</v>
-      </c>
-      <c r="G45" t="n">
-        <v>34.52256</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>17.11028</v>
-      </c>
-      <c r="D46" t="n">
-        <v>16.22348</v>
-      </c>
-      <c r="E46" t="n">
-        <v>16.95727</v>
-      </c>
-      <c r="F46" t="n">
-        <v>22.17912</v>
-      </c>
-      <c r="G46" t="n">
-        <v>34.81056</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>17.07182</v>
-      </c>
-      <c r="D47" t="n">
-        <v>16.22476</v>
-      </c>
-      <c r="E47" t="n">
-        <v>16.67679</v>
-      </c>
-      <c r="F47" t="n">
-        <v>22.25914</v>
-      </c>
-      <c r="G47" t="n">
-        <v>34.8121</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>17.03713</v>
-      </c>
-      <c r="D48" t="n">
-        <v>16.57743</v>
-      </c>
-      <c r="E48" t="n">
-        <v>16.36412</v>
-      </c>
-      <c r="F48" t="n">
-        <v>22.2468</v>
-      </c>
-      <c r="G48" t="n">
-        <v>34.1545</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>17.25904</v>
-      </c>
-      <c r="D49" t="n">
-        <v>16.41273</v>
-      </c>
-      <c r="E49" t="n">
-        <v>16.47779</v>
-      </c>
-      <c r="F49" t="n">
-        <v>22.4021</v>
-      </c>
-      <c r="G49" t="n">
-        <v>34.26884</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>16.72628</v>
-      </c>
-      <c r="D50" t="n">
-        <v>16.1187</v>
-      </c>
-      <c r="E50" t="n">
-        <v>16.60687</v>
-      </c>
-      <c r="F50" t="n">
-        <v>22.09374</v>
-      </c>
-      <c r="G50" t="n">
-        <v>34.24909</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.6162300000000001</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1.11949</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.62148</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1.14149</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.61775</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1.12204</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>0.6112</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1.13238</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0.62185</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1.14747</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>0.61902</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1.13733</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0.61168</v>
-      </c>
-      <c r="D58" t="n">
-        <v>1.13083</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>0.6152</v>
-      </c>
-      <c r="D59" t="n">
-        <v>1.12715</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>0.61516</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1.11803</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>via 2</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>0.61834</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1.13307</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>0.62083</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1.12324</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>0.6121</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1.13801</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>0.6008599999999999</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1.13533</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>0.61295</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1.14456</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>0.62329</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1.12792</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>0.62188</v>
-      </c>
-      <c r="D68" t="n">
-        <v>1.12366</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>0.60519</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1.13752</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>0.61158</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1.13187</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>0.75956</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0.08415</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0.61285</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0.96169</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0.1112</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.00768</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0.09365</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0.1263</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>0.76068</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0.08186</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0.61788</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0.98171</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0.11364</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.00773</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0.09483999999999999</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0.12905</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>0.76167</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0.08122</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0.6132</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0.98441</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0.11088</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0.09383</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0.13004</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>0.77346</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0.08216</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0.61654</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0.96883</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0.11066</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0.00773</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0.0951</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0.12778</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>0.7658199999999999</v>
-      </c>
-      <c r="D76" t="n">
-        <v>0.08148</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0.60168</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0.96394</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0.11245</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.00766</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0.09414</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0.12642</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>0.75543</v>
-      </c>
-      <c r="D77" t="n">
-        <v>0.08376</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0.61997</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0.98193</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0.11238</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.007820000000000001</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0.09465999999999999</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0.13059</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>0.7708199999999999</v>
-      </c>
-      <c r="D78" t="n">
-        <v>0.08377</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0.62483</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0.11013</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0.00775</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0.09372999999999999</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0.13065</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>0.74818</v>
-      </c>
-      <c r="D79" t="n">
-        <v>0.08187999999999999</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0.63079</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0.97797</v>
-      </c>
-      <c r="G79" t="n">
-        <v>0.11172</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.00775</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0.09268999999999999</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0.12693</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>0.76118</v>
-      </c>
-      <c r="D80" t="n">
-        <v>0.08218</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0.6216</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.9837900000000001</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0.11213</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.00772</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0.09490999999999999</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0.12765</v>
+        <v>0.11206</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09368</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12912</v>
       </c>
     </row>
   </sheetData>
